--- a/config/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
+++ b/config/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B4B773-8496-49E4-995E-55F0362554B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FC48AE-027C-4180-80BB-A11C616E385A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -234,9 +232,6 @@
     <t>O47</t>
   </si>
   <si>
-    <t>E266</t>
-  </si>
-  <si>
     <t>A25</t>
   </si>
   <si>
@@ -256,6 +251,9 @@
   </si>
   <si>
     <t>J25</t>
+  </si>
+  <si>
+    <t>E270</t>
   </si>
 </sst>
 </file>
@@ -593,14 +591,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="35.77734375" customWidth="1"/>
-    <col min="3" max="5" width="20.77734375" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" customWidth="1"/>
+    <col min="3" max="5" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -617,7 +615,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -625,7 +623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -633,7 +631,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -641,7 +639,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -652,11 +650,11 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
@@ -667,11 +665,11 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -682,11 +680,11 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -697,11 +695,11 @@
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
@@ -712,11 +710,11 @@
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -727,11 +725,11 @@
         <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>48</v>
       </c>
@@ -742,11 +740,11 @@
         <v>36</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -754,7 +752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
@@ -762,7 +760,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
@@ -770,7 +768,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -781,10 +779,10 @@
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -792,7 +790,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>50</v>
       </c>
@@ -803,7 +801,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -814,7 +812,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
@@ -825,7 +823,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>41</v>
       </c>
@@ -836,7 +834,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>42</v>
       </c>
@@ -847,7 +845,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -864,7 +862,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>52</v>
       </c>
@@ -875,7 +873,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>54</v>
       </c>
@@ -886,7 +884,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>56</v>
       </c>
@@ -897,7 +895,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>43</v>
       </c>
@@ -914,52 +912,52 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42"/>
     </row>
   </sheetData>

--- a/config/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
+++ b/config/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FC48AE-027C-4180-80BB-A11C616E385A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0AB3FB-ADE3-440B-855E-B8E09E2CCF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -253,7 +253,7 @@
     <t>J25</t>
   </si>
   <si>
-    <t>E270</t>
+    <t>E271</t>
   </si>
 </sst>
 </file>

--- a/config/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
+++ b/config/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0AB3FB-ADE3-440B-855E-B8E09E2CCF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B940B8BC-E015-4523-B2F9-713F941679C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -253,7 +253,7 @@
     <t>J25</t>
   </si>
   <si>
-    <t>E271</t>
+    <t>E270</t>
   </si>
 </sst>
 </file>
